--- a/eval_output/營業部_劉祐誠_評分表.xlsx
+++ b/eval_output/營業部_劉祐誠_評分表.xlsx
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -164,6 +164,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -178,6 +181,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -634,7 +641,7 @@
         </is>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIF(D6:P6,"&lt;&gt;")</f>
+        <f>COUNTIF(D6:D6,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -694,23 +701,25 @@
 0~10分</t>
         </is>
       </c>
+      <c r="D8" s="10" t="n"/>
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="9" t="n"/>
       <c r="H8" s="9" t="n"/>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>公司辦法考核</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>根據考核固定成績</t>
         </is>
       </c>
-      <c r="G9" s="10" t="n"/>
-      <c r="H9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="11" t="n"/>
     </row>
     <row r="10" ht="115.5" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -718,12 +727,12 @@
           <t>團隊溝通協調能力20%</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>受評者的溝通協調與配合度</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>✓非常願意溝通協調且配合度極高 (16-20)
 ✓願意溝通協調且配合度高 (12-15)
@@ -732,18 +741,19 @@
 ✓非常不願意溝通協調且配合度極低 (0-3)</t>
         </is>
       </c>
+      <c r="D10" s="10" t="n"/>
       <c r="F10" s="3" t="n"/>
-      <c r="G10" s="10" t="n"/>
+      <c r="G10" s="11" t="n"/>
       <c r="H10" s="9" t="n"/>
     </row>
     <row r="11" ht="65" customHeight="1">
       <c r="A11" s="8" t="n"/>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>※印象中你對受評者在指導與覆核部屬方面，願意給幾分</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">✓經常主動指導(領導)部屬 (10)
 ✓需經部屬提出並樂意指導(領導) (5-9)
@@ -752,33 +762,34 @@
 </t>
         </is>
       </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="F11" s="15" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="F11" s="17" t="n"/>
       <c r="G11" s="9" t="n"/>
-      <c r="H11" s="16" t="n"/>
+      <c r="H11" s="18" t="n"/>
     </row>
     <row r="12" ht="38" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>領導統御
 30%</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>*低於等於3分或高於等於10分，請說明原因：________________</t>
         </is>
       </c>
+      <c r="D12" s="10" t="n"/>
       <c r="G12" s="9" t="n"/>
       <c r="H12" s="9" t="n"/>
     </row>
     <row r="13" ht="76" customHeight="1">
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>是否落實公司 ISO9001 及內部稽核／內控制度之執行</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>✓完整落實ISO9001與內稽內控機制，文件、流程、紀錄皆符合規範，並主動優化制度或提出改善措施(10)
 ✓大致落實制度要求，稽核資料齊全，偶有小缺失但能即時改善(8-9)
@@ -788,28 +799,29 @@
 ✓無執行相關制度或嚴重違反規範(0)</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n"/>
+      <c r="D13" s="16" t="n"/>
       <c r="G13" s="9" t="n"/>
       <c r="H13" s="9" t="n"/>
     </row>
     <row r="14" ht="43.5" customHeight="1">
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>*低於等於3分或最高分，請敘述狀況：_________________________</t>
         </is>
       </c>
-      <c r="F14" s="15" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="F14" s="17" t="n"/>
       <c r="G14" s="9" t="n"/>
-      <c r="H14" s="16" t="n"/>
+      <c r="H14" s="18" t="n"/>
     </row>
     <row r="15" ht="126" customHeight="1">
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>※受評者是否能有效辨識部屬專長、適切分配工作並透過指導與激勵促進部屬成長之管理能力評價
 共評者可依據主管平日之部屬培育、工作指導、績效追蹤、溝通協調、團隊管理及人才發展情形進行評分。</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>✓受評者具備良好人才辨識與培育能力，能依部屬特性有效授權、指導及激勵，並建立正向團隊文化與人才發展機制。(10)
 ✓受評者能適度掌握部屬能力並進行工作安排與培育，團隊運作及人才發展狀況良好。(7-9)
@@ -817,18 +829,19 @@
 ✓受評者未能有效掌握部屬特性與發展需求，團隊管理、人才培育及激勵成效不佳。(1-3)</t>
         </is>
       </c>
+      <c r="D15" s="10" t="n"/>
       <c r="G15" s="9" t="n"/>
       <c r="H15" s="9" t="n"/>
     </row>
     <row r="16" ht="57" customHeight="1">
       <c r="A16" s="8" t="n"/>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">你對於受評者在會議追蹤事項之執行、回覆與結案管理上，是否能依規定期限完成並有效追蹤事項進度之表現評價為何？
 </t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>10分：會議追蹤事項皆能準時完成並主動追蹤，結案完整無需提醒
 7~9分：大多能準時完成，偶有延遲但能主動回覆並完成結案
@@ -836,31 +849,32 @@
 4分以下：經常延遲、未追蹤或未完成結案，影響會議執行成效或跨部門作業效率</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n"/>
+      <c r="D16" s="16" t="n"/>
       <c r="G16" s="9" t="n"/>
       <c r="H16" s="9" t="n"/>
     </row>
     <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>工作態度30%</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>*低於等於4分或高於等於9分，請說明原因：____________________</t>
         </is>
       </c>
+      <c r="D17" s="10" t="n"/>
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="6" t="n"/>
     </row>
     <row r="18" ht="54" customHeight="1">
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>你對於受評者完成工作之品質與完整性評價為何？</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>10分：工作完整且品質穩定，可直接使用
 7~9分：大致完整，少量修正即可
@@ -868,22 +882,23 @@
 4分以下：經常缺漏或品質不佳</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n"/>
+      <c r="D18" s="16" t="n"/>
     </row>
     <row r="19" ht="57.5" customHeight="1">
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>*低於等於4分或高於等於9分，請說明原因：____________________</t>
         </is>
       </c>
+      <c r="D19" s="10" t="n"/>
     </row>
     <row r="20" ht="57.5" customHeight="1">
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>你對於受評者在工作目標、交辦事項及時程管理上的達成能力評價為何？</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>10分：能有效規劃並穩定達成目標
 7~9分：大多能如期完成
@@ -891,23 +906,24 @@
 4分以下：經常未完成或需他人協助追蹤</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n"/>
+      <c r="D20" s="16" t="n"/>
     </row>
     <row r="21" ht="64" customHeight="1">
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>*低於等於4分或高於等於9分，請說明原因：____________________</t>
         </is>
       </c>
+      <c r="D21" s="10" t="n"/>
     </row>
     <row r="22" ht="50.5" customHeight="1">
-      <c r="B22" s="22" t="n"/>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="B22" s="24" t="n"/>
+      <c r="C22" s="25" t="inlineStr">
         <is>
           <t>總分</t>
         </is>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="26">
         <f>SUM(D8:D21)</f>
         <v/>
       </c>
@@ -925,6 +941,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="19">
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="D11:D12"/>
